--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -79,67 +79,70 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>DEL CARMEN</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ROQUE</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
   </si>
   <si>
     <t>AULIS</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>SERRANO</t>
   </si>
   <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
     <t>CONCEPCION</t>
   </si>
   <si>
-    <t>PERLA</t>
+    <t>KARLA MICHEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ADAN</t>
   </si>
   <si>
     <t>ALDO</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -546,10 +549,10 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>17</v>
@@ -558,7 +561,7 @@
         <v>77.27</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -572,10 +575,10 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -584,7 +587,7 @@
         <v>87.09999999999999</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -598,19 +601,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>57.89</v>
+        <v>60.53</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -624,19 +627,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>68.56999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -650,19 +653,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>63.64</v>
+        <v>69.7</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -715,16 +718,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>59.09</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -738,16 +744,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>70.97</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -761,16 +770,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>42.11</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -784,16 +796,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>74.29000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -807,16 +822,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>54.55</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -869,19 +887,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>77.27</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -895,19 +913,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>87.09999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -921,19 +939,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>57.89</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -947,19 +965,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>68.56999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -973,10 +991,10 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>21</v>
@@ -985,7 +1003,7 @@
         <v>63.64</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1027,140 +1045,140 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920284</v>
+        <v>19330051920045</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920377</v>
+        <v>19330051920284</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920319</v>
+        <v>19330051920289</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920426</v>
+        <v>19330051920323</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920375</v>
+        <v>19330051920352</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920369</v>
+        <v>19330051920319</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1168,13 +1186,13 @@
         <v>19330051920253</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1183,7 +1201,7 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1191,13 +1209,13 @@
         <v>19330051920433</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1206,7 +1224,7 @@
         <v>13</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -79,76 +79,82 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>AULIS</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>KARLA MICHEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
   </si>
   <si>
     <t>EUSEBIO</t>
   </si>
   <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>KARLA MICHEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
     <t>ALDO</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1045,16 +1051,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>18330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1063,7 +1069,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1074,10 +1080,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1097,10 +1103,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1120,10 +1126,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1143,10 +1149,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1160,71 +1166,94 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920319</v>
+        <v>19330051920433</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920253</v>
+        <v>19330051920045</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920433</v>
+        <v>19330051920319</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920253</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>13</v>
       </c>
-      <c r="G9">
-        <v>4</v>
+      <c r="G10">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
@@ -1092,7 +1092,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1115,7 +1115,7 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -100,9 +100,6 @@
     <t>CHAVEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>AULIS</t>
-  </si>
-  <si>
     <t>JOSUE YAMIN</t>
   </si>
   <si>
@@ -149,9 +143,6 @@
   </si>
   <si>
     <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ALDO</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -607,16 +598,16 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>60.53</v>
+        <v>63.16</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -776,16 +767,16 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>13</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>42.11</v>
+        <v>44.74</v>
       </c>
       <c r="H4">
         <v>7.7</v>
@@ -945,16 +936,16 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -1019,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1057,10 +1048,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1080,10 +1071,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1103,10 +1094,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1126,10 +1117,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1149,10 +1140,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1172,10 +1163,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1195,10 +1186,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1212,47 +1203,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920319</v>
+        <v>19330051920253</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920253</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -79,73 +79,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>GALVEZ</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>KARLA MICHEL</t>
+    <t>MARTI NEFTALI</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
     <t>ADAN</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
 </sst>
 </file>
@@ -546,19 +540,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>77.27</v>
+        <v>90.91</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -572,19 +566,19 @@
         <v>31</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>87.09999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -598,10 +592,10 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <v>24</v>
@@ -610,7 +604,7 @@
         <v>63.16</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -624,10 +618,10 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>29</v>
@@ -636,7 +630,7 @@
         <v>82.86</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -650,19 +644,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -715,16 +709,16 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>6</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>59.09</v>
+        <v>72.73</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -741,19 +735,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -767,19 +761,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>44.74</v>
+        <v>52.63</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -793,10 +787,10 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>26</v>
@@ -805,7 +799,7 @@
         <v>74.29000000000001</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -819,19 +813,19 @@
         <v>33</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>12</v>
       </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
       <c r="F6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -884,19 +878,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -910,19 +904,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -936,19 +930,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>52.63</v>
+        <v>55.26</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -962,19 +956,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>77.14</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -988,19 +982,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,16 +1036,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920078</v>
+        <v>19330051920418</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1060,44 +1054,44 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920284</v>
+        <v>19330051920081</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920289</v>
+        <v>19330051920286</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1111,22 +1105,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920323</v>
+        <v>19330051920443</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1134,16 +1128,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920352</v>
+        <v>19330051920323</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1157,71 +1151,48 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920433</v>
+        <v>19330051920358</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920045</v>
+        <v>19330051920352</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920253</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
